--- a/SQExcel.Portal/src/content/docs/ja/docs/images/quick-start/quick-start.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/quick-start/quick-start.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\quick-start\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\quick-start\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C9522B-40C2-476D-927A-C3C3EE1D1077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B735A63-428F-4A3B-B1BF-EEED8A57CF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="200" windowWidth="22540" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="23268" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QUICK-START" sheetId="1" r:id="rId1"/>
@@ -757,169 +757,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>154060</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12072997-2081-0FEE-D336-61B063CA0BAB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="8229600"/>
-          <a:ext cx="10801350" cy="8155060"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7471</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>59766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>4483</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>162958</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="94" name="グループ化 93">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{383128FB-C957-77B9-798D-1611E37DA91A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="239059" y="754531"/>
-          <a:ext cx="10650071" cy="7282427"/>
-          <a:chOff x="242421" y="745566"/>
-          <a:chExt cx="10804712" cy="7189792"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="2" name="図 1">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22C2BE5F-50F3-62C2-2358-741DB3EACDB4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="242421" y="745566"/>
-            <a:ext cx="10804712" cy="7189792"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="正方形/長方形 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65992D3D-8A78-4E9B-AF7E-78B6DED4115B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6955491" y="1816847"/>
-            <a:ext cx="3971738" cy="1113117"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>1078</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>216648</xdr:rowOff>
@@ -943,8 +780,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="232666" y="17817354"/>
-          <a:ext cx="8477681" cy="4773705"/>
+          <a:off x="234160" y="17930907"/>
+          <a:ext cx="8531469" cy="4805081"/>
           <a:chOff x="236029" y="16675848"/>
           <a:chExt cx="8140219" cy="4459940"/>
         </a:xfrm>
@@ -963,7 +800,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -1094,171 +931,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>64330</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>218390</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7" name="グループ化 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9229A0EE-AF15-A6D0-799E-6616A9652976}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="23454742"/>
-          <a:ext cx="10650071" cy="8259648"/>
-          <a:chOff x="234950" y="21735148"/>
-          <a:chExt cx="10801350" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="6" name="図 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D6EB7D7-FCF1-2DED-FC2E-36BF72B7C365}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="21735148"/>
-            <a:ext cx="10801350" cy="8155060"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="正方形/長方形 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D81BAF-84D6-07C6-CF5C-76A9B815981C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5030276" y="27070756"/>
-            <a:ext cx="1640964" cy="117646"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="正方形/長方形 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401D6CC8-5CA0-41D6-9871-90BAD5E2693A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3768019" y="26733938"/>
-            <a:ext cx="6687331" cy="1630931"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>18142</xdr:colOff>
       <xdr:row>140</xdr:row>
       <xdr:rowOff>36285</xdr:rowOff>
@@ -1282,8 +954,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249730" y="32458638"/>
-          <a:ext cx="8520057" cy="3595572"/>
+          <a:off x="251224" y="32667814"/>
+          <a:ext cx="8573845" cy="3617985"/>
           <a:chOff x="253092" y="30897285"/>
           <a:chExt cx="8641080" cy="3550749"/>
         </a:xfrm>
@@ -1367,7 +1039,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -1641,270 +1313,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>194</xdr:row>
-      <xdr:rowOff>208488</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="38" name="グループ化 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEFBBB8-DEE8-A6B8-31BC-8AA67BE03B0C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="36876957"/>
-          <a:ext cx="10650071" cy="8259649"/>
-          <a:chOff x="234950" y="35030228"/>
-          <a:chExt cx="10801350" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="36" name="図 35">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F1A1B2-CC23-79E9-F87A-014C6C399A0B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="35030228"/>
-            <a:ext cx="10801350" cy="8155060"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="正方形/長方形 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{630CF150-34A5-4307-8A8B-82CFAE42FF49}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4952092" y="42802628"/>
-            <a:ext cx="1617364" cy="355601"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="正方形/長方形 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC718E0B-6876-4089-86E4-32FB1D9C1477}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="575069" y="36078685"/>
-            <a:ext cx="1889417" cy="210535"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="37" name="正方形/長方形 36">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7738D98-32E8-4147-AE1F-4BB32694CA04}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5024664" y="40359693"/>
-            <a:ext cx="1640816" cy="118545"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>198</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>227</xdr:row>
-      <xdr:rowOff>137131</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="図 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20FBABB6-D328-D7C2-09DF-A5117F68CD90}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="43891200"/>
-          <a:ext cx="10801350" cy="6766531"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>231587</xdr:colOff>
       <xdr:row>252</xdr:row>
@@ -1929,8 +1337,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231587" y="58457354"/>
-          <a:ext cx="8520057" cy="3673884"/>
+          <a:off x="231587" y="58833872"/>
+          <a:ext cx="8575339" cy="3697790"/>
           <a:chOff x="249890" y="57622143"/>
           <a:chExt cx="8641080" cy="3629060"/>
         </a:xfrm>
@@ -1949,7 +1357,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2080,409 +1488,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>14942</xdr:colOff>
-      <xdr:row>327</xdr:row>
-      <xdr:rowOff>74706</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>197822</xdr:colOff>
-      <xdr:row>347</xdr:row>
-      <xdr:rowOff>151788</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="69" name="グループ化 68">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C454EC6-DC81-22F1-3589-17DA6A8C79AA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="246530" y="75804059"/>
-          <a:ext cx="8520057" cy="4708847"/>
-          <a:chOff x="249892" y="72083706"/>
-          <a:chExt cx="8641080" cy="4649082"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="63" name="図 62">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD7673EB-30A8-68E0-3171-A5FD2AB93ADA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="249892" y="72083706"/>
-            <a:ext cx="8641080" cy="4649082"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="64" name="正方形/長方形 63">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4F1CD3-3AD7-48B2-819D-F3BF4A1ACE66}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="411941" y="74467578"/>
-            <a:ext cx="4979641" cy="236116"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="65" name="正方形/長方形 64">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A44190EE-5F2E-9705-3093-9C12A69F9DBD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="397210" y="75679981"/>
-            <a:ext cx="2482110" cy="228551"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="66" name="正方形/長方形 65">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B92FA52B-E466-02B4-B841-C7A0A42FC065}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6022985" y="76388331"/>
-            <a:ext cx="1284908" cy="289083"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="68" name="正方形/長方形 67">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7D5575-176A-6DE2-2240-A6D699C60214}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2379206" y="75188556"/>
-            <a:ext cx="1432288" cy="294267"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>209176</xdr:colOff>
-      <xdr:row>351</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>206188</xdr:colOff>
-      <xdr:row>376</xdr:row>
-      <xdr:rowOff>10086</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="95" name="グループ化 94">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5088A7B5-B540-DCB4-CF36-3C8B592A5509}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="209176" y="81414471"/>
-          <a:ext cx="10650071" cy="5672791"/>
-          <a:chOff x="209176" y="80365600"/>
-          <a:chExt cx="10804712" cy="5598086"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="70" name="図 69">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{157B46FE-7AF5-77F2-06B7-BD75CF776D6B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="209176" y="80365600"/>
-            <a:ext cx="10804712" cy="5598086"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="正方形/長方形 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E35B9C-0EA7-4C0A-9361-1593C88356C7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1021975" y="85476976"/>
-            <a:ext cx="3714377" cy="277907"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>271</xdr:row>
       <xdr:rowOff>67239</xdr:rowOff>
@@ -2506,8 +1511,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="62827651"/>
-          <a:ext cx="8516695" cy="2332926"/>
+          <a:off x="233082" y="63232557"/>
+          <a:ext cx="8570483" cy="2347867"/>
           <a:chOff x="234950" y="62017839"/>
           <a:chExt cx="8637718" cy="2303044"/>
         </a:xfrm>
@@ -2526,7 +1531,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2735,8 +1740,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="53496882"/>
-          <a:ext cx="8520057" cy="4153410"/>
+          <a:off x="233082" y="53842024"/>
+          <a:ext cx="8573845" cy="4178810"/>
           <a:chOff x="234950" y="51206400"/>
           <a:chExt cx="8641080" cy="4102610"/>
         </a:xfrm>
@@ -2755,7 +1760,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2942,312 +1947,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>380</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>402</xdr:row>
-      <xdr:rowOff>165594</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="48" name="グループ化 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EAF4AF-BE96-185C-5BB5-96894F31A636}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="88003529"/>
-          <a:ext cx="10650071" cy="5260536"/>
-          <a:chOff x="234950" y="83667600"/>
-          <a:chExt cx="10801350" cy="5194794"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="26" name="図 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51AB6939-84C0-ADFE-EFB9-79BAFAE03927}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="83667600"/>
-            <a:ext cx="10801350" cy="5194794"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="正方形/長方形 30">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C6E0478-5EC7-4539-8D55-0CC9204C332A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2771214" y="88381541"/>
-            <a:ext cx="667498" cy="315259"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="32" name="正方形/長方形 31">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6E43C2-5C1A-4A82-8804-32E288F086B7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1432112" y="85732470"/>
-            <a:ext cx="9510058" cy="715683"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="33" name="吹き出し: 四角形 32">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{022C1843-0A13-4164-A944-EDC2C18EFF45}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5627969" y="86826166"/>
-            <a:ext cx="2640105" cy="352610"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -35818"/>
-              <a:gd name="adj2" fmla="val -111481"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>空白行（ここでデータ取り込みを終了）</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="47" name="吹き出し: 四角形 46">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B51788C-A82D-46E5-8DD0-701608140E86}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="921497" y="86714107"/>
-            <a:ext cx="2375274" cy="295836"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 37152"/>
-              <a:gd name="adj2" fmla="val -171527"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>新規に追加する取引先データ </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>2</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>件</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>406</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -3270,8 +1969,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="94024824"/>
-          <a:ext cx="10650071" cy="5260535"/>
+          <a:off x="233082" y="94631435"/>
+          <a:ext cx="10717306" cy="5293406"/>
           <a:chOff x="234950" y="89382600"/>
           <a:chExt cx="10801350" cy="5194794"/>
         </a:xfrm>
@@ -3290,7 +1989,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3475,125 +2174,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>432</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>460</xdr:row>
-      <xdr:rowOff>108688</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="43" name="グループ化 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488D7250-9834-0FF1-5AB8-A036FD8E051B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="100046119"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="234950" y="98755201"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="40" name="図 39">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90EBB695-973A-5EC6-A78A-5F3621B04D83}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="98755201"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="75" name="正方形/長方形 74">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44F63790-A4B0-47A4-AC90-36755F0CB9EE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8562652" y="99599892"/>
-            <a:ext cx="2195003" cy="440703"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>119310</xdr:colOff>
       <xdr:row>459</xdr:row>
@@ -3664,125 +2244,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>507</xdr:row>
-      <xdr:rowOff>36286</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>530</xdr:row>
-      <xdr:rowOff>192847</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="85" name="グループ化 84">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86236ED4-BC38-2D3A-840E-FB72FBC6AEB0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="117451521"/>
-          <a:ext cx="10650071" cy="5483091"/>
-          <a:chOff x="234950" y="111556800"/>
-          <a:chExt cx="10801350" cy="5414362"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="83" name="図 82">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349D3FB3-FEF3-2EB0-C030-17C9C52E7023}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="111556800"/>
-            <a:ext cx="10801350" cy="5414362"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="84" name="正方形/長方形 83">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1508366C-5639-4DDC-AB08-647BEC7ABDBE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="443592" y="113028185"/>
-            <a:ext cx="4129315" cy="192315"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>226786</xdr:colOff>
       <xdr:row>534</xdr:row>
@@ -3807,8 +2268,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="226786" y="123767904"/>
-          <a:ext cx="10645802" cy="7279150"/>
+          <a:off x="226786" y="124565762"/>
+          <a:ext cx="10714531" cy="7325468"/>
           <a:chOff x="234950" y="117500400"/>
           <a:chExt cx="10801350" cy="7186516"/>
         </a:xfrm>
@@ -3827,7 +2288,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3904,345 +2365,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>466</xdr:row>
-      <xdr:rowOff>54426</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>503</xdr:row>
-      <xdr:rowOff>127079</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="92" name="グループ化 91">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C7FB18C-1733-6983-4D69-6993FE830F7A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="231588" y="107974544"/>
-          <a:ext cx="8520057" cy="8641417"/>
-          <a:chOff x="234950" y="102467226"/>
-          <a:chExt cx="8641080" cy="8530853"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="89" name="図 88">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2433DC2-8EF7-B33B-FB2A-B10143B59BB7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="102467226"/>
-            <a:ext cx="8641080" cy="8513545"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="79" name="正方形/長方形 78">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F0D5DC7-675F-4733-A2DD-9E1889DD6CC2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="407891" y="104843561"/>
-            <a:ext cx="5177583" cy="347423"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="80" name="正方形/長方形 79">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D5BD3FA-1787-4EB0-8A1D-1928396990ED}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="426101" y="106562656"/>
-            <a:ext cx="839560" cy="329409"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="81" name="正方形/長方形 80">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B72D1CA-28E1-4E42-9165-929C5E2C3F0E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6126363" y="110650667"/>
-            <a:ext cx="1247501" cy="347412"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="90" name="正方形/長方形 89">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDFB3520-C907-670E-6B00-F2E8F795D380}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="389749" y="105592861"/>
-            <a:ext cx="5493072" cy="366867"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="91" name="正方形/長方形 90">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C17AD5A0-4F26-5992-0A17-6B9F12DE5920}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4564487" y="106142973"/>
-            <a:ext cx="2104827" cy="337250"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>569</xdr:row>
       <xdr:rowOff>27215</xdr:rowOff>
     </xdr:from>
@@ -4266,7 +2388,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4275,50 +2397,6 @@
         <a:xfrm>
           <a:off x="235857" y="124532572"/>
           <a:ext cx="10842172" cy="6979849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7471</xdr:colOff>
-      <xdr:row>295</xdr:row>
-      <xdr:rowOff>14941</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>4483</xdr:colOff>
-      <xdr:row>323</xdr:row>
-      <xdr:rowOff>123627</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4705BD1F-021D-ACA1-3F53-C361D51E72CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="239059" y="68333470"/>
-          <a:ext cx="10650071" cy="6593157"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4354,7 +2432,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4369,6 +2447,2516 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>59766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>4483</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>162958</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="16" name="グループ化 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE542773-7715-89EA-D354-DA81AAFCB3F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="240553" y="759013"/>
+          <a:ext cx="10718801" cy="7328745"/>
+          <a:chOff x="243691" y="745566"/>
+          <a:chExt cx="10863132" cy="7189792"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="94" name="グループ化 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{383128FB-C957-77B9-798D-1611E37DA91A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="243691" y="745566"/>
+            <a:ext cx="10863132" cy="7189792"/>
+            <a:chOff x="242421" y="745566"/>
+            <a:chExt cx="10804712" cy="7189792"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="図 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22C2BE5F-50F3-62C2-2358-741DB3EACDB4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="242421" y="745566"/>
+              <a:ext cx="10804712" cy="7189792"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="正方形/長方形 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65992D3D-8A78-4E9B-AF7E-78B6DED4115B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6955491" y="1816847"/>
+              <a:ext cx="3971738" cy="1113117"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="15" name="図 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{009ADA8B-8F30-4DD2-99E1-17C9B7619924}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="370691" y="820269"/>
+            <a:ext cx="236219" cy="239195"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>154060</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="52" name="グループ化 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9CF58D1-7153-E821-0C08-252CFD07E500}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="8857129"/>
+          <a:ext cx="10717306" cy="8311943"/>
+          <a:chOff x="236220" y="8686800"/>
+          <a:chExt cx="10858500" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="図 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12072997-2081-0FEE-D336-61B063CA0BAB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="236220" y="8686800"/>
+            <a:ext cx="10858500" cy="8155060"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="49" name="図 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C7C4402-A8BD-4A2E-BB16-674958632A08}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="290649" y="8741228"/>
+            <a:ext cx="243950" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>64330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>218390</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="58" name="グループ化 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41AF9076-B568-662C-ACEE-78751669157B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="23605648"/>
+          <a:ext cx="10717306" cy="8311942"/>
+          <a:chOff x="236220" y="23152930"/>
+          <a:chExt cx="10858500" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9229A0EE-AF15-A6D0-799E-6616A9652976}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="23152930"/>
+            <a:ext cx="10858500" cy="8155060"/>
+            <a:chOff x="234950" y="21735148"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="図 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D6EB7D7-FCF1-2DED-FC2E-36BF72B7C365}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="21735148"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="正方形/長方形 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D81BAF-84D6-07C6-CF5C-76A9B815981C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5030276" y="27070756"/>
+              <a:ext cx="1640964" cy="117646"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401D6CC8-5CA0-41D6-9871-90BAD5E2693A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3768019" y="26733938"/>
+              <a:ext cx="6687331" cy="1630931"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="53" name="図 52">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552D05BA-43C7-4320-B014-23826A8B9B15}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="301534" y="23197457"/>
+            <a:ext cx="243950" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>208488</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="61" name="グループ化 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A7CB02B-C2C5-68E6-4292-2E717CDD40DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="37114522"/>
+          <a:ext cx="10717306" cy="8311942"/>
+          <a:chOff x="236220" y="36401828"/>
+          <a:chExt cx="10858500" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="38" name="グループ化 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEFBBB8-DEE8-A6B8-31BC-8AA67BE03B0C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="36401828"/>
+            <a:ext cx="10858500" cy="8155060"/>
+            <a:chOff x="234950" y="35030228"/>
+            <a:chExt cx="10801350" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="36" name="図 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19F1A1B2-CC23-79E9-F87A-014C6C399A0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="35030228"/>
+              <a:ext cx="10801350" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="正方形/長方形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{630CF150-34A5-4307-8A8B-82CFAE42FF49}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4952092" y="42802628"/>
+              <a:ext cx="1617364" cy="355601"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="正方形/長方形 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC718E0B-6876-4089-86E4-32FB1D9C1477}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="575069" y="36078685"/>
+              <a:ext cx="1889417" cy="210535"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="37" name="正方形/長方形 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7738D98-32E8-4147-AE1F-4BB32694CA04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5024664" y="40359693"/>
+              <a:ext cx="1640816" cy="118545"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="60" name="図 59">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{830ECD7E-FFA7-4B91-ADE3-0D692D18771C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="301535" y="36456256"/>
+            <a:ext cx="243950" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>227</xdr:row>
+      <xdr:rowOff>137131</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="77" name="グループ化 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{696B39E7-6D9B-EBD1-6DE8-7BF1ECF506DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="46150306"/>
+          <a:ext cx="10717306" cy="6896519"/>
+          <a:chOff x="236220" y="45262800"/>
+          <a:chExt cx="10858500" cy="6766531"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="39" name="図 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20FBABB6-D328-D7C2-09DF-A5117F68CD90}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="236220" y="45262800"/>
+            <a:ext cx="10858500" cy="6766531"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="73" name="図 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD7507BC-EFB0-4CFA-878F-4BFC7DF3D968}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="268876" y="45284572"/>
+            <a:ext cx="206314" cy="219106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>295</xdr:row>
+      <xdr:rowOff>14941</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>4483</xdr:colOff>
+      <xdr:row>323</xdr:row>
+      <xdr:rowOff>123627</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="96" name="グループ化 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF35805-3CFE-D7BF-9D5F-6D02AB9F6BCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="240553" y="68774235"/>
+          <a:ext cx="10718801" cy="6634992"/>
+          <a:chOff x="243691" y="67451941"/>
+          <a:chExt cx="10863132" cy="6509486"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="11" name="図 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4705BD1F-021D-ACA1-3F53-C361D51E72CD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="243691" y="67451941"/>
+            <a:ext cx="10863132" cy="6509486"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="82" name="図 81">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDFC479E-3B6F-4CCC-9B48-842DDC4B1068}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="290648" y="67469657"/>
+            <a:ext cx="206314" cy="219106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>14942</xdr:colOff>
+      <xdr:row>327</xdr:row>
+      <xdr:rowOff>74706</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>197822</xdr:colOff>
+      <xdr:row>347</xdr:row>
+      <xdr:rowOff>151788</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="98" name="グループ化 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2724130D-DDBE-86D5-34FF-F4F6BE92CDFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="248024" y="76292635"/>
+          <a:ext cx="8573845" cy="4738729"/>
+          <a:chOff x="251162" y="74826906"/>
+          <a:chExt cx="8686800" cy="4649082"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="69" name="グループ化 68">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C454EC6-DC81-22F1-3589-17DA6A8C79AA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="251162" y="74826906"/>
+            <a:ext cx="8686800" cy="4649082"/>
+            <a:chOff x="249892" y="72083706"/>
+            <a:chExt cx="8641080" cy="4649082"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="63" name="図 62">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD7673EB-30A8-68E0-3171-A5FD2AB93ADA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="249892" y="72083706"/>
+              <a:ext cx="8641080" cy="4649082"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="64" name="正方形/長方形 63">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4F1CD3-3AD7-48B2-819D-F3BF4A1ACE66}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="411941" y="74467578"/>
+              <a:ext cx="4979641" cy="236116"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="65" name="正方形/長方形 64">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A44190EE-5F2E-9705-3093-9C12A69F9DBD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="397210" y="75679981"/>
+              <a:ext cx="2482110" cy="228551"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="66" name="正方形/長方形 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B92FA52B-E466-02B4-B841-C7A0A42FC065}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6022985" y="76388331"/>
+              <a:ext cx="1284908" cy="289083"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="68" name="正方形/長方形 67">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7D5575-176A-6DE2-2240-A6D699C60214}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2379206" y="75188556"/>
+              <a:ext cx="1432288" cy="294267"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="97" name="図 96">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF1386A-923D-4B70-83E9-311D109A8A29}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="345077" y="74882829"/>
+            <a:ext cx="206314" cy="219106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>432</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>460</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="100" name="グループ化 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6B00F9A-A450-777C-C986-DACDB87A8377}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="100691577"/>
+          <a:ext cx="10717306" cy="6634993"/>
+          <a:chOff x="236220" y="98755201"/>
+          <a:chExt cx="10858500" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="43" name="グループ化 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488D7250-9834-0FF1-5AB8-A036FD8E051B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="98755201"/>
+            <a:ext cx="10858500" cy="6509487"/>
+            <a:chOff x="234950" y="98755201"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="40" name="図 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90EBB695-973A-5EC6-A78A-5F3621B04D83}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="98755201"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="75" name="正方形/長方形 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44F63790-A4B0-47A4-AC90-36755F0CB9EE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8562652" y="99599892"/>
+              <a:ext cx="2195003" cy="440703"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="99" name="図 98">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF590FC9-C8BD-4DD6-975F-D3D1BA7B2C5F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="290648" y="98787857"/>
+            <a:ext cx="206314" cy="219106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>466</xdr:row>
+      <xdr:rowOff>54426</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>503</xdr:row>
+      <xdr:rowOff>127079</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="102" name="グループ化 101">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A11FF38D-EE9D-1A80-C4C2-9816B3CA81D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="108670802"/>
+          <a:ext cx="8573845" cy="8696701"/>
+          <a:chOff x="236220" y="106582026"/>
+          <a:chExt cx="8686800" cy="8530853"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="92" name="グループ化 91">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C7FB18C-1733-6983-4D69-6993FE830F7A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="106582026"/>
+            <a:ext cx="8686800" cy="8530853"/>
+            <a:chOff x="234950" y="102467226"/>
+            <a:chExt cx="8641080" cy="8530853"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="89" name="図 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2433DC2-8EF7-B33B-FB2A-B10143B59BB7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="102467226"/>
+              <a:ext cx="8641080" cy="8513545"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="79" name="正方形/長方形 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F0D5DC7-675F-4733-A2DD-9E1889DD6CC2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="407891" y="104843561"/>
+              <a:ext cx="5177583" cy="347423"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="80" name="正方形/長方形 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D5BD3FA-1787-4EB0-8A1D-1928396990ED}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="426101" y="106562656"/>
+              <a:ext cx="839560" cy="329409"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="81" name="正方形/長方形 80">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B72D1CA-28E1-4E42-9165-929C5E2C3F0E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6126363" y="110650667"/>
+              <a:ext cx="1247501" cy="347412"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="90" name="正方形/長方形 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDFB3520-C907-670E-6B00-F2E8F795D380}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="389749" y="105592861"/>
+              <a:ext cx="5493072" cy="366867"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="91" name="正方形/長方形 90">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C17AD5A0-4F26-5992-0A17-6B9F12DE5920}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4564487" y="106142973"/>
+              <a:ext cx="2104827" cy="337250"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="101" name="図 100">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0BF6194-CC4F-416E-BA22-8F4D5CDA683C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="268877" y="106636457"/>
+            <a:ext cx="243950" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>209176</xdr:colOff>
+      <xdr:row>351</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>206188</xdr:colOff>
+      <xdr:row>376</xdr:row>
+      <xdr:rowOff>10086</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="104" name="グループ化 103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC3946A8-B24E-B292-9B8C-10F4E219FD6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="209176" y="81938906"/>
+          <a:ext cx="10718800" cy="5710145"/>
+          <a:chOff x="209176" y="80365600"/>
+          <a:chExt cx="10863132" cy="5598086"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="95" name="グループ化 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5088A7B5-B540-DCB4-CF36-3C8B592A5509}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="209176" y="80365600"/>
+            <a:ext cx="10863132" cy="5598086"/>
+            <a:chOff x="209176" y="80365600"/>
+            <a:chExt cx="10804712" cy="5598086"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="70" name="図 69">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{157B46FE-7AF5-77F2-06B7-BD75CF776D6B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="209176" y="80365600"/>
+              <a:ext cx="10804712" cy="5598086"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="正方形/長方形 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E35B9C-0EA7-4C0A-9361-1593C88356C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1021975" y="85476976"/>
+              <a:ext cx="3714377" cy="277907"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="103" name="図 102">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6373074F-9833-EB64-4B19-2114918594DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5265421" y="81503520"/>
+            <a:ext cx="3230879" cy="179041"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>380</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>402</xdr:row>
+      <xdr:rowOff>165594</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="106" name="グループ化 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F89B217-B452-D1FB-38FA-621EC9B7B0A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="88571294"/>
+          <a:ext cx="10717306" cy="5293406"/>
+          <a:chOff x="236220" y="86868000"/>
+          <a:chExt cx="10858500" cy="5194794"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="48" name="グループ化 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EAF4AF-BE96-185C-5BB5-96894F31A636}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="86868000"/>
+            <a:ext cx="10858500" cy="5194794"/>
+            <a:chOff x="234950" y="83667600"/>
+            <a:chExt cx="10801350" cy="5194794"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="26" name="図 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51AB6939-84C0-ADFE-EFB9-79BAFAE03927}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="83667600"/>
+              <a:ext cx="10801350" cy="5194794"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="正方形/長方形 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C6E0478-5EC7-4539-8D55-0CC9204C332A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2771214" y="88381541"/>
+              <a:ext cx="667498" cy="315259"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="32" name="正方形/長方形 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6E43C2-5C1A-4A82-8804-32E288F086B7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1432112" y="85732470"/>
+              <a:ext cx="9510058" cy="715683"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="33" name="吹き出し: 四角形 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{022C1843-0A13-4164-A944-EDC2C18EFF45}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5627969" y="86826166"/>
+              <a:ext cx="2640105" cy="352610"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -35818"/>
+                <a:gd name="adj2" fmla="val -111481"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>空白行（ここでデータ取り込みを終了）</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="47" name="吹き出し: 四角形 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B51788C-A82D-46E5-8DD0-701608140E86}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="921497" y="86714107"/>
+              <a:ext cx="2375274" cy="295836"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 37152"/>
+                <a:gd name="adj2" fmla="val -171527"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>新規に追加する取引先データ </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>件</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="105" name="図 104">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47212F19-C5BB-0BED-9CE0-3C073B1731EB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6446521" y="87934801"/>
+            <a:ext cx="2369820" cy="155520"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>507</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>530</xdr:row>
+      <xdr:rowOff>192847</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="108" name="グループ化 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7EDF15E-91F3-BE77-0515-4705FFA118E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="118209039"/>
+          <a:ext cx="10717306" cy="5517455"/>
+          <a:chOff x="236220" y="115936486"/>
+          <a:chExt cx="10858500" cy="5414361"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="85" name="グループ化 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86236ED4-BC38-2D3A-840E-FB72FBC6AEB0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="115936486"/>
+            <a:ext cx="10858500" cy="5414361"/>
+            <a:chOff x="234950" y="111556800"/>
+            <a:chExt cx="10801350" cy="5414362"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="83" name="図 82">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349D3FB3-FEF3-2EB0-C030-17C9C52E7023}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="111556800"/>
+              <a:ext cx="10801350" cy="5414362"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="84" name="正方形/長方形 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1508366C-5639-4DDC-AB08-647BEC7ABDBE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="443592" y="113028185"/>
+              <a:ext cx="4129315" cy="192315"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="107" name="図 106">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B63781D-3D72-4556-AAB4-E0D09999C4BB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7513319" y="117241320"/>
+            <a:ext cx="2750821" cy="180568"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4638,9 +5226,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B569"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -4648,12 +5236,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -4661,12 +5249,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>33</v>
       </c>
@@ -4674,12 +5262,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -4687,12 +5275,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4700,12 +5288,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>33</v>
       </c>
@@ -4713,12 +5301,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>33</v>
       </c>
@@ -4726,12 +5314,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B198" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>33</v>
       </c>
@@ -4739,12 +5327,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B231" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>33</v>
       </c>
@@ -4752,12 +5340,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>33</v>
       </c>
@@ -4765,12 +5353,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B271" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>33</v>
       </c>
@@ -4778,12 +5366,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B285" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>33</v>
       </c>
@@ -4791,12 +5379,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B295" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>33</v>
       </c>
@@ -4804,12 +5392,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B327" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>33</v>
       </c>
@@ -4817,12 +5405,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>33</v>
       </c>
@@ -4830,17 +5418,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B379" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B380" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>33</v>
       </c>
@@ -4848,12 +5436,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B406" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>33</v>
       </c>
@@ -4861,12 +5449,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B432" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>33</v>
       </c>
@@ -4874,17 +5462,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B465" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="466" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B466" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>33</v>
       </c>
@@ -4892,12 +5480,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>33</v>
       </c>
@@ -4905,12 +5493,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B534" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>33</v>
       </c>
@@ -4918,7 +5506,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B569" t="s">
         <v>22</v>
       </c>
